--- a/Priyas Expense Summary.xlsx
+++ b/Priyas Expense Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FCE9F0-C9B0-4A1C-8351-0442F75E7A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A323E4-9B40-4C66-AE5B-89B92FAD1716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Expense" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Expense!$A$1:$C$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Expense!$A$1:$D$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -117,22 +117,13 @@
     <t>Task to Perform</t>
   </si>
   <si>
-    <t>Q1: How many times has Priya done transactions on online shopping, ordering food and gifts?</t>
-  </si>
-  <si>
     <t>Total Expense</t>
-  </si>
-  <si>
-    <t>Q2: Calculate the total expenses against each distinct item.</t>
   </si>
   <si>
     <t>Total Expenses</t>
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>Q3: Arrange the item-wise total expense in descending order.</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -153,26 +144,53 @@
     <t>Cost Type</t>
   </si>
   <si>
-    <t>Q4: Present the item-wise total expense through a chart that shows the expense of each item as a percentage of the total expense. Don’t take trip expenses into consideration.</t>
-  </si>
-  <si>
     <t>Expenses</t>
   </si>
   <si>
     <t>Percentage</t>
   </si>
   <si>
-    <t>Q6: Add a new column to the data table, name it as “Category” and apply data validation with drop-down fields as “Essentials” and “Non-essentials”. Fill in the column.</t>
+    <t>Descending order</t>
   </si>
   <si>
-    <t>Q7: Add another new column and name it as “Cost Type”. For each item, if the expense is more than 2000, tag it as “Over budget”, else, tag it as “Within budget”.</t>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>Q: Present the expense pattern visually over 3 months.</t>
+  </si>
+  <si>
+    <t>Q: Present the item-wise total expense through a chart that shows the expense of each item as a percentage of the total expense. Don’t take trip expenses into consideration.</t>
+  </si>
+  <si>
+    <t>Q: Add another new column and name it as “Cost Type”. For each item, if the expense is more than 2000, tag it as “Over budget”, else, tag it as “Within budget”.</t>
+  </si>
+  <si>
+    <t>Q: Add a new column to the data table, name it as “Category” and apply data validation with drop-down fields as “Essentials” and “Non-essentials”. Fill in the column.</t>
+  </si>
+  <si>
+    <t>Q: Arrange the item-wise total expense in descending order.</t>
+  </si>
+  <si>
+    <t>Q: Calculate the total expenses against each distinct item.</t>
+  </si>
+  <si>
+    <t>Q: How many times has Priya done transactions on online shopping, ordering food and gifts?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,8 +255,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,6 +312,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -327,7 +382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -371,26 +426,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -399,9 +434,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -415,7 +447,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -431,11 +462,59 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1110,9 +1189,331 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.41504855643044625"/>
+          <c:y val="4.6296296296296294E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent1"/>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$B$23:$B$25</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$23:$C$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>17443.37</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18764.269999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20837.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A630-49AA-8DDF-4ACB2C504919}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="981530608"/>
+        <c:axId val="981527728"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="981530608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="981527728"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="981527728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="981530608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
   <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -1592,7 +1993,600 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="100" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1193800</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D912E13E-78C6-153B-9E15-C23998A6E0A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2794000" y="5016500"/>
+          <a:ext cx="1041400" cy="6350"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1625,6 +2619,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>31749</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>422274</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{163728A2-273C-5A49-B23F-D17429091270}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1896,587 +2926,792 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.08984375" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" style="11" customWidth="1"/>
+    <col min="1" max="2" width="17.08984375" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>44470</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="str">
+        <f>TEXT(A2,"mmmm")</f>
+        <v>October</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9">
+      <c r="D2" s="9">
         <v>2300</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>44470</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="str">
+        <f t="shared" ref="B3:B51" si="0">TEXT(A3,"mmmm")</f>
+        <v>October</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9">
+      <c r="D3" s="9">
         <v>767</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>44470</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="10">
+      <c r="D4" s="10">
         <v>2500</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>44473</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9">
+      <c r="D5" s="9">
         <v>710</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>44473</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="9">
+      <c r="D6" s="9">
         <v>760</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>44476</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="10">
+      <c r="D7" s="10">
         <v>1900</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>44477</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="9">
+      <c r="D8" s="9">
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>44484</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="9">
+      <c r="D9" s="9">
         <v>620</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>44485</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="9">
+      <c r="D10" s="9">
         <v>470</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>44487</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="9">
+      <c r="D11" s="9">
         <v>970</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>44487</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="10">
+      <c r="D12" s="10">
         <v>1075</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>44488</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="9">
+      <c r="D13" s="9">
         <v>489</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>44491</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="10">
+      <c r="D14" s="10">
         <v>1574.1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>44491</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="9">
+      <c r="D15" s="9">
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>44494</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="9">
+      <c r="D16" s="9">
         <v>423</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>44496</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="9">
+      <c r="D17" s="9">
         <v>358.22</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>44496</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="9">
+      <c r="D18" s="9">
         <v>520</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>44497</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="9">
+      <c r="D19" s="9">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>44498</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="9">
+      <c r="D20" s="9">
         <v>407.05</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>44499</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>October</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="9">
+      <c r="D21" s="9">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>44501</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="10">
+      <c r="D22" s="10">
         <v>2327</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>44502</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="9">
+      <c r="D23" s="9">
         <v>1150</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>44504</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="10">
+      <c r="D24" s="10">
         <v>1138</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>44505</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="9">
+      <c r="D25" s="9">
         <v>500</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>44508</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="9">
+      <c r="D26" s="9">
         <v>702</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>44509</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="10">
+      <c r="D27" s="10">
         <v>1600</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>44512</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="9">
+      <c r="D28" s="9">
         <v>600</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>44515</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="9">
+      <c r="D29" s="9">
         <v>900</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>44515</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="9">
+      <c r="D30" s="9">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>44515</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="9">
+      <c r="D31" s="9">
         <v>2100</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>44517</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="9">
+      <c r="D32" s="9">
         <v>470.63</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>44517</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="9">
+      <c r="D33" s="9">
         <v>322.64</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>44518</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="9">
+      <c r="D34" s="9">
         <v>428</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>44519</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="9">
+      <c r="D35" s="9">
         <v>447</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>44522</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="10">
+      <c r="D36" s="10">
         <v>1720</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>44524</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="9">
+      <c r="D37" s="9">
         <v>540</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>44525</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="9">
+      <c r="D38" s="9">
         <v>314</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>44526</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="9">
+      <c r="D39" s="9">
         <v>518</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>44526</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="10">
+      <c r="D40" s="10">
         <v>2000</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>44529</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="9">
+      <c r="D41" s="9">
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>44530</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>November</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="9">
+      <c r="D42" s="9">
         <v>500</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>44531</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="10">
+      <c r="D43" s="10">
         <v>2500</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>44534</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="9">
+      <c r="D44" s="9">
         <v>710</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>44537</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="9">
+      <c r="D45" s="9">
         <v>2300</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>44539</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="9">
+      <c r="D46" s="9">
         <v>12000</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>44545</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="9">
+      <c r="D47" s="9">
         <v>1500</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>44547</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="9">
+      <c r="D48" s="9">
         <v>470.63</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>44550</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="9">
+      <c r="D49" s="9">
         <v>267</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>44553</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C50" s="9">
+      <c r="D50" s="9">
         <v>640</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>44553</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>December</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="9">
+      <c r="D51" s="9">
         <v>450</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="31" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" ht="31" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
-      <c r="C52" s="11">
-        <f>SUM(C2:C51)</f>
+      <c r="B52" s="2"/>
+      <c r="D52" s="11">
+        <f>SUM(D2:D51)</f>
         <v>57045.27</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2555,30 +3790,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="A1" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2">
-        <f>COUNTIF(Expense!B1:B51,B2)</f>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="31">
+        <f>COUNTIF(Expense!C1:C51,B2)</f>
         <v>6</v>
       </c>
     </row>
@@ -2586,13 +3821,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3">
-        <f>COUNTIF(Expense!B2:B52,B3)</f>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="31">
+        <f>COUNTIF(Expense!C2:C52,B3)</f>
         <v>5</v>
       </c>
     </row>
@@ -2600,357 +3835,360 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4">
-        <f>COUNTIF(Expense!B3:B53,B4)</f>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="31">
+        <f>COUNTIF(Expense!C3:C53,B4)</f>
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5">
+      <c r="B5" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="31">
         <f>SUM(E2:E4)</f>
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="43">
+        <v>7775</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="43">
+        <v>7464</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="43">
+        <v>10194.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="43">
+        <v>3217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="43">
+        <v>3342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="43">
+        <v>5688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="43">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="43">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="43">
+        <v>1411.26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="43">
+        <v>1510.9099999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="43">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>7775</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>7464</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>10194.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12">
-        <v>3217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13">
-        <v>3342</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14">
-        <v>5688</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16">
-        <v>2586</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17">
-        <v>1411.26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18">
-        <v>1510.9099999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="17">
+      <c r="B20" s="45">
         <f>SUM(B9:B19)</f>
         <v>57045.270000000004</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
+      <c r="A22" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="14" t="s">
+      <c r="B23" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="15" t="s">
-        <v>27</v>
+      <c r="E23" s="37" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="35">
         <v>7775</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="20">
         <v>3217</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="35">
         <v>7464</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="20">
         <v>12000</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="35">
         <v>10194.1</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="20">
         <v>10194.1</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="35">
         <v>3217</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="20">
         <v>1857</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="35">
         <v>3342</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="20">
         <v>7464</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="35">
         <v>5688</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="20">
         <v>2586</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="35">
         <v>1857</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="20">
         <v>1411.26</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="35">
         <v>2586</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="20">
         <v>7775</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="35">
         <v>1411.26</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="20">
         <v>5688</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="35">
         <v>1510.9099999999999</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="20">
         <v>3342</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="35">
         <v>12000</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="20">
         <v>1510.9099999999999</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35">
+      <c r="A35" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="35">
         <f>SUM(B24:B34)</f>
         <v>57045.270000000004</v>
       </c>
-      <c r="D35" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35">
+      <c r="D35" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="20">
         <f>SUM(E24:E34)</f>
         <v>57045.270000000004</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
+      <c r="A37" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D24:E34">
@@ -2968,6 +4206,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2986,1416 +4225,1362 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="33"/>
+      <c r="D2" s="23" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="34">
+      <c r="A3" s="24">
         <v>44470</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="25">
         <v>2300</v>
       </c>
-      <c r="D3" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="33"/>
+      <c r="D3" s="29" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="36">
+      <c r="A4" s="26">
         <v>44470</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="25">
         <v>767</v>
       </c>
-      <c r="D4" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="33"/>
+      <c r="D4" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="36">
+      <c r="A5" s="26">
         <v>44470</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="27">
         <v>2500</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="33"/>
+      <c r="D5" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="36">
+      <c r="A6" s="26">
         <v>44473</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="25">
         <v>710</v>
       </c>
-      <c r="D6" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="33"/>
+      <c r="D6" s="29" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="34">
+      <c r="A7" s="24">
         <v>44473</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="25">
         <v>760</v>
       </c>
-      <c r="D7" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="33"/>
+      <c r="D7" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="36">
+      <c r="A8" s="26">
         <v>44476</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="27">
         <v>1900</v>
       </c>
-      <c r="D8" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="33"/>
+      <c r="D8" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="34">
+      <c r="A9" s="24">
         <v>44477</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="25">
         <v>450</v>
       </c>
-      <c r="D9" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="33"/>
+      <c r="D9" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="36">
+      <c r="A10" s="26">
         <v>44484</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="25">
         <v>620</v>
       </c>
-      <c r="D10" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="33"/>
+      <c r="D10" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="36">
+      <c r="A11" s="26">
         <v>44485</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="25">
         <v>470</v>
       </c>
-      <c r="D11" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="33"/>
+      <c r="D11" s="29" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="36">
+      <c r="A12" s="26">
         <v>44487</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="25">
         <v>970</v>
       </c>
-      <c r="D12" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="33"/>
+      <c r="D12" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="36">
+      <c r="A13" s="26">
         <v>44487</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="27">
         <v>1075</v>
       </c>
-      <c r="D13" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="33"/>
+      <c r="D13" s="29" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="36">
+      <c r="A14" s="26">
         <v>44488</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="25">
         <v>489</v>
       </c>
-      <c r="D14" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="33"/>
+      <c r="D14" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="36">
+      <c r="A15" s="26">
         <v>44491</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="27">
         <v>1574.1</v>
       </c>
-      <c r="D15" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="33"/>
+      <c r="D15" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="36">
+      <c r="A16" s="26">
         <v>44491</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="25">
         <v>550</v>
       </c>
-      <c r="D16" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="33"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="36">
+      <c r="D16" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="26">
         <v>44494</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="25">
         <v>423</v>
       </c>
-      <c r="D17" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="33"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="36">
+      <c r="D17" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="26">
         <v>44496</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="25">
         <v>358.22</v>
       </c>
-      <c r="D18" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="33"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="36">
+      <c r="D18" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="26">
         <v>44496</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="25">
         <v>520</v>
       </c>
-      <c r="D19" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="33"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="34">
+      <c r="D19" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="24">
         <v>44497</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="25">
         <v>300</v>
       </c>
-      <c r="D20" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="33"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="34">
+      <c r="D20" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="24">
         <v>44498</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="25">
         <v>407.05</v>
       </c>
-      <c r="D21" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="33"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="34">
+      <c r="D21" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="24">
         <v>44499</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="25">
         <v>300</v>
       </c>
-      <c r="D22" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="33"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="36">
+      <c r="D22" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="26">
         <v>44501</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="27">
         <v>2327</v>
       </c>
-      <c r="D23" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="33"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="36">
+      <c r="D23" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="26">
         <v>44502</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="25">
         <v>1150</v>
       </c>
-      <c r="D24" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="33"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="36">
+      <c r="D24" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="26">
         <v>44504</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="27">
         <v>1138</v>
       </c>
-      <c r="D25" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="33"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="34">
+      <c r="D25" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="24">
         <v>44505</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="25">
         <v>500</v>
       </c>
-      <c r="D26" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="33"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="34">
+      <c r="D26" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="24">
         <v>44508</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="25">
         <v>702</v>
       </c>
-      <c r="D27" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="33"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="36">
+      <c r="D27" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="26">
         <v>44509</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="27">
         <v>1600</v>
       </c>
-      <c r="D28" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="33"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="36">
+      <c r="D28" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="26">
         <v>44512</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="25">
         <v>600</v>
       </c>
-      <c r="D29" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29" s="33"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="34">
+      <c r="D29" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="24">
         <v>44515</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="25">
         <v>900</v>
       </c>
-      <c r="D30" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="33"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="36">
+      <c r="D30" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="26">
         <v>44515</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="25">
         <v>150</v>
       </c>
-      <c r="D31" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="33"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="34">
+      <c r="D31" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="24">
         <v>44515</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="25">
         <v>2100</v>
       </c>
-      <c r="D32" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="33"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="34">
+      <c r="D32" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="24">
         <v>44517</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="25">
         <v>470.63</v>
       </c>
-      <c r="D33" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="33"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="34">
+      <c r="D33" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="24">
         <v>44517</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="25">
         <v>322.64</v>
       </c>
-      <c r="D34" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="33"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="34">
+      <c r="D34" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="24">
         <v>44518</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="25">
         <v>428</v>
       </c>
-      <c r="D35" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="33"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="34">
+      <c r="D35" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="24">
         <v>44519</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="25">
         <v>447</v>
       </c>
-      <c r="D36" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E36" s="33"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="34">
+      <c r="D36" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="24">
         <v>44522</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="37">
+      <c r="C37" s="27">
         <v>1720</v>
       </c>
-      <c r="D37" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="33"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="36">
+      <c r="D37" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="26">
         <v>44524</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="25">
         <v>540</v>
       </c>
-      <c r="D38" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="33"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="34">
+      <c r="D38" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="24">
         <v>44525</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="25">
         <v>314</v>
       </c>
-      <c r="D39" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E39" s="33"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="34">
+      <c r="D39" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="24">
         <v>44526</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="35">
+      <c r="C40" s="25">
         <v>518</v>
       </c>
-      <c r="D40" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E40" s="33"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="34">
+      <c r="D40" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="24">
         <v>44526</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="37">
+      <c r="C41" s="27">
         <v>2000</v>
       </c>
-      <c r="D41" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="33"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="36">
+      <c r="D41" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="26">
         <v>44529</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="25">
         <v>337</v>
       </c>
-      <c r="D42" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E42" s="33"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="34">
+      <c r="D42" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="24">
         <v>44530</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="35">
+      <c r="C43" s="25">
         <v>500</v>
       </c>
-      <c r="D43" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E43" s="33"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="34">
+      <c r="D43" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="24">
         <v>44531</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="37">
+      <c r="C44" s="27">
         <v>2500</v>
       </c>
-      <c r="D44" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E44" s="33"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="36">
+      <c r="D44" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="26">
         <v>44534</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="25">
         <v>710</v>
       </c>
-      <c r="D45" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E45" s="33"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="34">
+      <c r="D45" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="24">
         <v>44537</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="35">
+      <c r="C46" s="25">
         <v>2300</v>
       </c>
-      <c r="D46" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" s="33"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="34">
+      <c r="D46" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="24">
         <v>44539</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="25">
         <v>12000</v>
       </c>
-      <c r="D47" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" s="33"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="34">
+      <c r="D47" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="24">
         <v>44545</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="35">
+      <c r="C48" s="25">
         <v>1500</v>
       </c>
-      <c r="D48" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E48" s="33"/>
+      <c r="D48" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A49" s="34">
+      <c r="A49" s="24">
         <v>44547</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="25">
         <v>470.63</v>
       </c>
-      <c r="D49" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E49" s="33"/>
+      <c r="D49" s="29" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A50" s="34">
+      <c r="A50" s="24">
         <v>44550</v>
       </c>
-      <c r="B50" s="24" t="s">
+      <c r="B50" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="35">
+      <c r="C50" s="25">
         <v>267</v>
       </c>
-      <c r="D50" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E50" s="33"/>
+      <c r="D50" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A51" s="34">
+      <c r="A51" s="24">
         <v>44553</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="25">
         <v>640</v>
       </c>
-      <c r="D51" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E51" s="33"/>
+      <c r="D51" s="29" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A52" s="34">
+      <c r="A52" s="24">
         <v>44553</v>
       </c>
-      <c r="B52" s="24" t="s">
+      <c r="B52" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="35">
+      <c r="C52" s="25">
         <v>450</v>
       </c>
-      <c r="D52" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E52" s="33"/>
+      <c r="D52" s="29" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="53" spans="1:11" ht="31" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
-      <c r="B53" s="33"/>
       <c r="C53" s="11">
         <f>SUM(C3:C52)</f>
         <v>57045.27</v>
       </c>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A55" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="39"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
+      <c r="A55" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="48"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="32" t="s">
-        <v>35</v>
+      <c r="C56" s="23" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A57" s="24" t="s">
+      <c r="A57" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="25">
         <v>2300</v>
       </c>
-      <c r="C57" s="41" t="str">
+      <c r="C57" s="30" t="str">
         <f>IF(B57&gt;2000,"over budget","within budget")</f>
         <v>over budget</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B58" s="35">
+      <c r="B58" s="25">
         <v>767</v>
       </c>
-      <c r="C58" s="41" t="str">
+      <c r="C58" s="30" t="str">
         <f t="shared" ref="C58:C106" si="0">IF(B58&gt;2000,"over budget","within budget")</f>
         <v>within budget</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B59" s="37">
+      <c r="B59" s="27">
         <v>2500</v>
       </c>
-      <c r="C59" s="41" t="str">
+      <c r="C59" s="30" t="str">
         <f t="shared" si="0"/>
         <v>over budget</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B60" s="35">
+      <c r="B60" s="25">
         <v>710</v>
       </c>
-      <c r="C60" s="41" t="str">
+      <c r="C60" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A61" s="24" t="s">
+      <c r="A61" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="35">
+      <c r="B61" s="25">
         <v>760</v>
       </c>
-      <c r="C61" s="41" t="str">
+      <c r="C61" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B62" s="37">
+      <c r="B62" s="27">
         <v>1900</v>
       </c>
-      <c r="C62" s="41" t="str">
+      <c r="C62" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A63" s="24" t="s">
+      <c r="A63" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B63" s="35">
+      <c r="B63" s="25">
         <v>450</v>
       </c>
-      <c r="C63" s="41" t="str">
+      <c r="C63" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="35">
+      <c r="B64" s="25">
         <v>620</v>
       </c>
-      <c r="C64" s="41" t="str">
+      <c r="C64" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="23" t="s">
+      <c r="A65" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="35">
+      <c r="B65" s="25">
         <v>470</v>
       </c>
-      <c r="C65" s="41" t="str">
+      <c r="C65" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B66" s="35">
+      <c r="B66" s="25">
         <v>970</v>
       </c>
-      <c r="C66" s="41" t="str">
+      <c r="C66" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="24" t="s">
+      <c r="A67" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="37">
+      <c r="B67" s="27">
         <v>1075</v>
       </c>
-      <c r="C67" s="41" t="str">
+      <c r="C67" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="35">
+      <c r="B68" s="25">
         <v>489</v>
       </c>
-      <c r="C68" s="41" t="str">
+      <c r="C68" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="23" t="s">
+      <c r="A69" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B69" s="37">
+      <c r="B69" s="27">
         <v>1574.1</v>
       </c>
-      <c r="C69" s="41" t="str">
+      <c r="C69" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B70" s="35">
+      <c r="B70" s="25">
         <v>550</v>
       </c>
-      <c r="C70" s="41" t="str">
+      <c r="C70" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B71" s="35">
+      <c r="B71" s="25">
         <v>423</v>
       </c>
-      <c r="C71" s="41" t="str">
+      <c r="C71" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B72" s="35">
+      <c r="B72" s="25">
         <v>358.22</v>
       </c>
-      <c r="C72" s="41" t="str">
+      <c r="C72" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="23" t="s">
+      <c r="A73" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B73" s="35">
+      <c r="B73" s="25">
         <v>520</v>
       </c>
-      <c r="C73" s="41" t="str">
+      <c r="C73" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="24" t="s">
+      <c r="A74" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B74" s="35">
+      <c r="B74" s="25">
         <v>300</v>
       </c>
-      <c r="C74" s="41" t="str">
+      <c r="C74" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="24" t="s">
+      <c r="A75" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B75" s="35">
+      <c r="B75" s="25">
         <v>407.05</v>
       </c>
-      <c r="C75" s="41" t="str">
+      <c r="C75" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="24" t="s">
+      <c r="A76" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B76" s="35">
+      <c r="B76" s="25">
         <v>300</v>
       </c>
-      <c r="C76" s="41" t="str">
+      <c r="C76" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B77" s="37">
+      <c r="B77" s="27">
         <v>2327</v>
       </c>
-      <c r="C77" s="41" t="str">
+      <c r="C77" s="30" t="str">
         <f t="shared" si="0"/>
         <v>over budget</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="35">
+      <c r="B78" s="25">
         <v>1150</v>
       </c>
-      <c r="C78" s="41" t="str">
+      <c r="C78" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="23" t="s">
+      <c r="A79" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B79" s="37">
+      <c r="B79" s="27">
         <v>1138</v>
       </c>
-      <c r="C79" s="41" t="str">
+      <c r="C79" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="24" t="s">
+      <c r="A80" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B80" s="35">
+      <c r="B80" s="25">
         <v>500</v>
       </c>
-      <c r="C80" s="41" t="str">
+      <c r="C80" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="24" t="s">
+      <c r="A81" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B81" s="35">
+      <c r="B81" s="25">
         <v>702</v>
       </c>
-      <c r="C81" s="41" t="str">
+      <c r="C81" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="23" t="s">
+      <c r="A82" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B82" s="37">
+      <c r="B82" s="27">
         <v>1600</v>
       </c>
-      <c r="C82" s="41" t="str">
+      <c r="C82" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="23" t="s">
+      <c r="A83" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B83" s="35">
+      <c r="B83" s="25">
         <v>600</v>
       </c>
-      <c r="C83" s="41" t="str">
+      <c r="C83" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="24" t="s">
+      <c r="A84" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B84" s="35">
+      <c r="B84" s="25">
         <v>900</v>
       </c>
-      <c r="C84" s="41" t="str">
+      <c r="C84" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="24" t="s">
+      <c r="A85" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B85" s="35">
+      <c r="B85" s="25">
         <v>150</v>
       </c>
-      <c r="C85" s="41" t="str">
+      <c r="C85" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="24" t="s">
+      <c r="A86" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B86" s="35">
+      <c r="B86" s="25">
         <v>2100</v>
       </c>
-      <c r="C86" s="41" t="str">
+      <c r="C86" s="30" t="str">
         <f t="shared" si="0"/>
         <v>over budget</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="24" t="s">
+      <c r="A87" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B87" s="35">
+      <c r="B87" s="25">
         <v>470.63</v>
       </c>
-      <c r="C87" s="41" t="str">
+      <c r="C87" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="24" t="s">
+      <c r="A88" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="35">
+      <c r="B88" s="25">
         <v>322.64</v>
       </c>
-      <c r="C88" s="41" t="str">
+      <c r="C88" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="23" t="s">
+      <c r="A89" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B89" s="35">
+      <c r="B89" s="25">
         <v>428</v>
       </c>
-      <c r="C89" s="41" t="str">
+      <c r="C89" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="24" t="s">
+      <c r="A90" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B90" s="35">
+      <c r="B90" s="25">
         <v>447</v>
       </c>
-      <c r="C90" s="41" t="str">
+      <c r="C90" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="24" t="s">
+      <c r="A91" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B91" s="37">
+      <c r="B91" s="27">
         <v>1720</v>
       </c>
-      <c r="C91" s="41" t="str">
+      <c r="C91" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="23" t="s">
+      <c r="A92" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B92" s="35">
+      <c r="B92" s="25">
         <v>540</v>
       </c>
-      <c r="C92" s="41" t="str">
+      <c r="C92" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="24" t="s">
+      <c r="A93" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B93" s="35">
+      <c r="B93" s="25">
         <v>314</v>
       </c>
-      <c r="C93" s="41" t="str">
+      <c r="C93" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="24" t="s">
+      <c r="A94" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B94" s="35">
+      <c r="B94" s="25">
         <v>518</v>
       </c>
-      <c r="C94" s="41" t="str">
+      <c r="C94" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="23" t="s">
+      <c r="A95" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B95" s="37">
+      <c r="B95" s="27">
         <v>2000</v>
       </c>
-      <c r="C95" s="41" t="str">
+      <c r="C95" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B96" s="35">
+      <c r="B96" s="25">
         <v>337</v>
       </c>
-      <c r="C96" s="41" t="str">
+      <c r="C96" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="24" t="s">
+      <c r="A97" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B97" s="35">
+      <c r="B97" s="25">
         <v>500</v>
       </c>
-      <c r="C97" s="41" t="str">
+      <c r="C97" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="24" t="s">
+      <c r="A98" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B98" s="37">
+      <c r="B98" s="27">
         <v>2500</v>
       </c>
-      <c r="C98" s="41" t="str">
+      <c r="C98" s="30" t="str">
         <f t="shared" si="0"/>
         <v>over budget</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="23" t="s">
+      <c r="A99" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B99" s="35">
+      <c r="B99" s="25">
         <v>710</v>
       </c>
-      <c r="C99" s="41" t="str">
+      <c r="C99" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="24" t="s">
+      <c r="A100" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B100" s="35">
+      <c r="B100" s="25">
         <v>2300</v>
       </c>
-      <c r="C100" s="41" t="str">
+      <c r="C100" s="30" t="str">
         <f t="shared" si="0"/>
         <v>over budget</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="24" t="s">
+      <c r="A101" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B101" s="35">
+      <c r="B101" s="25">
         <v>12000</v>
       </c>
-      <c r="C101" s="41" t="str">
+      <c r="C101" s="30" t="str">
         <f t="shared" si="0"/>
         <v>over budget</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="23" t="s">
+      <c r="A102" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B102" s="35">
+      <c r="B102" s="25">
         <v>1500</v>
       </c>
-      <c r="C102" s="41" t="str">
+      <c r="C102" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="24" t="s">
+      <c r="A103" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B103" s="35">
+      <c r="B103" s="25">
         <v>470.63</v>
       </c>
-      <c r="C103" s="41" t="str">
+      <c r="C103" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="24" t="s">
+      <c r="A104" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B104" s="35">
+      <c r="B104" s="25">
         <v>267</v>
       </c>
-      <c r="C104" s="41" t="str">
+      <c r="C104" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="24" t="s">
+      <c r="A105" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B105" s="35">
+      <c r="B105" s="25">
         <v>640</v>
       </c>
-      <c r="C105" s="41" t="str">
+      <c r="C105" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="24" t="s">
+      <c r="A106" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B106" s="35">
+      <c r="B106" s="25">
         <v>450</v>
       </c>
-      <c r="C106" s="41" t="str">
+      <c r="C106" s="30" t="str">
         <f t="shared" si="0"/>
         <v>within budget</v>
       </c>
@@ -4416,203 +5601,397 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1955F8E3-73A2-4E9B-B4CF-C09F70FBC901}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="15" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B5" s="27" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="C5" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="20">
         <v>3217</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="21">
         <f>C6/$C$17</f>
         <v>5.6393807935346783E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="20">
         <v>12000</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="21">
         <f t="shared" ref="D7:D16" si="0">C7/$C$17</f>
         <v>0.2103592462617847</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="O7" s="46"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="20">
         <v>10194.1</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="21">
         <f t="shared" si="0"/>
         <v>0.17870193269310497</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B9" s="28" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="20">
         <v>1857</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="21">
         <f t="shared" si="0"/>
         <v>3.255309335901118E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B10" s="28" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="20">
         <v>7464</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="21">
         <f t="shared" si="0"/>
         <v>0.13084345117483009</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B11" s="28" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="20">
         <v>2586</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="21">
         <f t="shared" si="0"/>
         <v>4.5332417569414606E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B12" s="28" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="20">
         <v>1411.26</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="21">
         <f t="shared" si="0"/>
         <v>2.4739299156617191E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B13" s="28" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="20">
         <v>7775</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="21">
         <f t="shared" si="0"/>
         <v>0.136295261640448</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B14" s="28" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="20">
         <v>5688</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="21">
         <f t="shared" si="0"/>
         <v>9.971028272808595E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="28" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="20">
         <v>3342</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
         <v>5.8585050083907041E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="28" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="20">
         <v>1510.9099999999999</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="21">
         <f t="shared" si="0"/>
         <v>2.6486157397449424E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B17" s="25" t="s">
-        <v>28</v>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="C17">
         <f>SUM(C6:C16)</f>
         <v>57045.270000000004</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <f>SUMIF(Expense!$B$1:$B$51,Sheet3!B23,Expense!$D$1:$D$51)</f>
+        <v>17443.37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="6"/>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24">
+        <f>SUMIF(Expense!$B$1:$B$51,Sheet3!B24,Expense!$D$1:$D$51)</f>
+        <v>18764.269999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="6"/>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25">
+        <f>SUMIF(Expense!$B$1:$B$51,Sheet3!B25,Expense!$D$1:$D$51)</f>
+        <v>20837.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="6"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="6"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="4"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="4"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="4"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="4"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="4"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="6"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="4"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="6"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="4"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="4"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="4"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" s="4"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="4"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="6"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="4"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="4"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" s="6"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="4"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="4"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="6"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" s="4"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" s="4"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" s="4"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" s="4"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" s="4"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" s="4"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:I3"/>
+    <mergeCell ref="A21:G21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
